--- a/analyst/Tracy/rmonize/data_dictionary/DD_IDEFICS_TRACY.xlsx
+++ b/analyst/Tracy/rmonize/data_dictionary/DD_IDEFICS_TRACY.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\use-cases-harmonisation\analyst\Tracy\rmonize\data_dictionary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55B71597-8176-4ED1-B2FC-5C748AD6F8F6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9255ECC8-6916-43C8-9586-C996B86CBCA3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="61">
   <si>
     <t>index</t>
   </si>
@@ -68,18 +68,12 @@
     <t>phys_activ</t>
   </si>
   <si>
-    <t>atc_who_2010</t>
-  </si>
-  <si>
     <t>Age[years]</t>
   </si>
   <si>
     <t>Isced level:Maximum of both parents</t>
   </si>
   <si>
-    <t>ID of the participant</t>
-  </si>
-  <si>
     <t>migration_T3</t>
   </si>
   <si>
@@ -119,18 +113,12 @@
     <t>Physical activity[hours per week]</t>
   </si>
   <si>
-    <t>child's drug use,last 7 days - ATC code of drug</t>
-  </si>
-  <si>
     <t>occupst_1</t>
   </si>
   <si>
     <t>occupst_2</t>
   </si>
   <si>
-    <t>Employment status of parent</t>
-  </si>
-  <si>
     <t>Attend school or university</t>
   </si>
   <si>
@@ -161,9 +149,6 @@
     <t>On welfare(social assistance)</t>
   </si>
   <si>
-    <t>SED</t>
-  </si>
-  <si>
     <t>LPA</t>
   </si>
   <si>
@@ -182,9 +167,6 @@
     <t>Avg time in light PA (min./day)</t>
   </si>
   <si>
-    <t>Avg Sedentary time (min./day)</t>
-  </si>
-  <si>
     <t>chdiabet</t>
   </si>
   <si>
@@ -201,13 +183,34 @@
   </si>
   <si>
     <t>leis_activ</t>
+  </si>
+  <si>
+    <t>employment status of the first person filled in the questionnaire</t>
+  </si>
+  <si>
+    <t>employment status of the second person filled in the questionnaire</t>
+  </si>
+  <si>
+    <t>Use of  vitamin/multivitamin supplements in the last 7 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no </t>
+  </si>
+  <si>
+    <t xml:space="preserve">yes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID </t>
+  </si>
+  <si>
+    <t>MED_SUPPL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -236,24 +239,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -275,7 +260,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -294,16 +279,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -315,6 +290,13 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -654,7 +636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
@@ -676,14 +658,14 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C2" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -703,7 +685,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
@@ -714,7 +696,7 @@
         <v>13</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
         <v>7</v>
@@ -722,10 +704,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
@@ -736,108 +718,97 @@
         <v>14</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="12" t="s">
+    <row r="8" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" s="12" t="s">
+    <row r="9" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="12" t="s">
+    <row r="10" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B11" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B11" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="B12" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="B13" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B14" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B14" s="13" t="s">
+    <row r="15" spans="1:4" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B15" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B15" s="13" t="s">
+      <c r="C15" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B16" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D16" s="12" t="s">
+      <c r="D15" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -849,11 +820,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="15"/>
+    <col min="2" max="2" width="9.140625" style="9"/>
     <col min="3" max="3" width="27.85546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -861,7 +832,7 @@
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -872,7 +843,7 @@
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="15">
+      <c r="B2" s="9">
         <v>1</v>
       </c>
       <c r="C2" t="s">
@@ -883,7 +854,7 @@
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="9">
         <v>2</v>
       </c>
       <c r="C3" t="s">
@@ -894,352 +865,374 @@
       <c r="A4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="16">
+      <c r="B4" s="10">
         <v>0</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="10">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="10">
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="10">
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="10">
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="10">
         <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="16">
+      <c r="B10" s="10">
         <v>6</v>
       </c>
       <c r="C10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="10">
+        <v>1</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="10">
+        <v>2</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="10">
+        <v>3</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="10">
+        <v>4</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="10">
+        <v>5</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="10">
+        <v>6</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="10">
+        <v>7</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="10">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" s="10">
+        <v>9</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="10">
+        <v>10</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="10">
+        <v>1</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="10">
+        <v>2</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="10">
+        <v>3</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="10">
+        <v>4</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="10">
+        <v>5</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A26" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" s="10">
+        <v>6</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="10">
+        <v>7</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28" s="10">
+        <v>8</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" s="10">
+        <v>9</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" s="10">
+        <v>10</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B31" s="11">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32" s="11">
+        <v>1</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" s="11">
+        <v>2</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="16">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B34" s="3">
+        <v>0</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" s="3">
         <v>1</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="16">
-        <v>2</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="16">
-        <v>3</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="16">
-        <v>4</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" s="16">
-        <v>5</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" s="16">
-        <v>6</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="16">
-        <v>7</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" s="16">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B19" s="16">
-        <v>9</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B20" s="16">
-        <v>10</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B21" s="16">
+      <c r="C35" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B36" s="11">
         <v>1</v>
       </c>
-      <c r="C21" s="7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B22" s="16">
-        <v>2</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B23" s="16">
-        <v>3</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" s="16">
-        <v>4</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B25" s="16">
-        <v>5</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" s="16">
-        <v>6</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="16">
-        <v>7</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28" s="16">
-        <v>8</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B29" s="16">
-        <v>9</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="16">
-        <v>10</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B31" s="17">
+      <c r="C36" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B37" s="11">
         <v>0</v>
       </c>
-      <c r="C31" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B32" s="17">
-        <v>1</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B33" s="17">
-        <v>2</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B34" s="16">
-        <v>1</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B35" s="16">
-        <v>0</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>57</v>
+      <c r="C37" s="5" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/analyst/Tracy/rmonize/data_dictionary/DD_IDEFICS_TRACY.xlsx
+++ b/analyst/Tracy/rmonize/data_dictionary/DD_IDEFICS_TRACY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\use-cases-harmonisation\analyst\Tracy\rmonize\data_dictionary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9255ECC8-6916-43C8-9586-C996B86CBCA3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A893CAD-9B97-4521-B94C-3FB47154786E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="57">
   <si>
     <t>index</t>
   </si>
@@ -191,19 +191,7 @@
     <t>employment status of the second person filled in the questionnaire</t>
   </si>
   <si>
-    <t>Use of  vitamin/multivitamin supplements in the last 7 days</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no </t>
-  </si>
-  <si>
-    <t xml:space="preserve">yes </t>
-  </si>
-  <si>
     <t xml:space="preserve">ID </t>
-  </si>
-  <si>
-    <t>MED_SUPPL</t>
   </si>
 </sst>
 </file>
@@ -636,7 +624,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
@@ -663,7 +651,7 @@
         <v>10</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>7</v>
@@ -790,25 +778,14 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>56</v>
+        <v>48</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="B15" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -820,7 +797,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
@@ -1191,47 +1168,25 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B34" s="3">
+        <v>48</v>
+      </c>
+      <c r="B34" s="11">
+        <v>1</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B35" s="11">
         <v>0</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B35" s="3">
-        <v>1</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B36" s="11">
-        <v>1</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B37" s="11">
-        <v>0</v>
-      </c>
-      <c r="C37" s="5" t="s">
+      <c r="C35" s="5" t="s">
         <v>51</v>
       </c>
     </row>

--- a/analyst/Tracy/rmonize/data_dictionary/DD_IDEFICS_TRACY.xlsx
+++ b/analyst/Tracy/rmonize/data_dictionary/DD_IDEFICS_TRACY.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\use-cases-harmonisation\analyst\Tracy\rmonize\data_dictionary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A893CAD-9B97-4521-B94C-3FB47154786E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{329291C8-1897-485D-B601-406F96BAFC9A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Variables" sheetId="1" r:id="rId1"/>
@@ -77,9 +77,6 @@
     <t>migration_T3</t>
   </si>
   <si>
-    <t>Migration status of parents</t>
-  </si>
-  <si>
     <t>One parent migrant</t>
   </si>
   <si>
@@ -192,6 +189,9 @@
   </si>
   <si>
     <t xml:space="preserve">ID </t>
+  </si>
+  <si>
+    <t>Migration status of parents at follow up</t>
   </si>
 </sst>
 </file>
@@ -651,7 +651,7 @@
         <v>10</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>7</v>
@@ -692,10 +692,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
@@ -706,7 +706,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
         <v>12</v>
@@ -714,10 +714,10 @@
     </row>
     <row r="8" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>7</v>
@@ -725,10 +725,10 @@
     </row>
     <row r="9" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>7</v>
@@ -739,7 +739,7 @@
         <v>17</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>7</v>
@@ -747,10 +747,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B11" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>12</v>
@@ -758,10 +758,10 @@
     </row>
     <row r="12" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B12" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>12</v>
@@ -769,10 +769,10 @@
     </row>
     <row r="13" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B13" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>45</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>12</v>
@@ -780,10 +780,10 @@
     </row>
     <row r="14" spans="1:4" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>49</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>7</v>
@@ -846,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -857,7 +857,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -868,7 +868,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -879,7 +879,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -890,7 +890,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -901,7 +901,7 @@
         <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -912,227 +912,227 @@
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B11" s="10">
         <v>1</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B12" s="10">
         <v>2</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B13" s="10">
         <v>3</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B14" s="10">
         <v>4</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B15" s="10">
         <v>5</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B16" s="10">
         <v>6</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B17" s="10">
         <v>7</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B18" s="10">
         <v>8</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B19" s="10">
         <v>9</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B20" s="10">
         <v>10</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B21" s="10">
         <v>1</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="10">
         <v>2</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23" s="10">
         <v>3</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B24" s="10">
         <v>4</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B25" s="10">
         <v>5</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B26" s="10">
         <v>6</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B27" s="10">
         <v>7</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B28" s="10">
         <v>8</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B29" s="10">
         <v>9</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B30" s="10">
         <v>10</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -1143,7 +1143,7 @@
         <v>0</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -1154,7 +1154,7 @@
         <v>1</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -1165,29 +1165,29 @@
         <v>2</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B34" s="11">
         <v>1</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B35" s="11">
         <v>0</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/analyst/Tracy/rmonize/data_dictionary/DD_IDEFICS_TRACY.xlsx
+++ b/analyst/Tracy/rmonize/data_dictionary/DD_IDEFICS_TRACY.xlsx
@@ -1,27 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\use-cases-harmonisation\analyst\Tracy\rmonize\data_dictionary\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schwarz-f\Desktop\use-cases-harmonisation\analyst\Tracy\rmonize\data_dictionary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{329291C8-1897-485D-B601-406F96BAFC9A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81BEB005-0E9B-4F57-A632-8E0F13CA1044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Variables" sheetId="1" r:id="rId1"/>
     <sheet name="Categories" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="61">
   <si>
     <t>index</t>
   </si>
@@ -44,18 +49,6 @@
     <t>Sex of the child</t>
   </si>
   <si>
-    <t>Integer</t>
-  </si>
-  <si>
-    <t>male</t>
-  </si>
-  <si>
-    <t>female</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
     <t>age</t>
   </si>
   <si>
@@ -71,36 +64,18 @@
     <t>Age[years]</t>
   </si>
   <si>
-    <t>Isced level:Maximum of both parents</t>
-  </si>
-  <si>
     <t>migration_T3</t>
   </si>
   <si>
     <t>One parent migrant</t>
   </si>
   <si>
-    <t xml:space="preserve"> Early childhood education (and on-going education or no graduation (yet))</t>
-  </si>
-  <si>
     <t>Primary education</t>
   </si>
   <si>
     <t>Lower secondary education</t>
   </si>
   <si>
-    <t xml:space="preserve"> Upper secondary education</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Post-secondary non-tertiary education</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Short-cycle tertiary education</t>
-  </si>
-  <si>
-    <t>Bachelors and higher levels</t>
-  </si>
-  <si>
     <t>Both parents non-migrant</t>
   </si>
   <si>
@@ -173,15 +148,6 @@
     <t>yes</t>
   </si>
   <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>Leisure activity [hours per week]</t>
-  </si>
-  <si>
-    <t>leis_activ</t>
-  </si>
-  <si>
     <t>employment status of the first person filled in the questionnaire</t>
   </si>
   <si>
@@ -192,6 +158,57 @@
   </si>
   <si>
     <t>Migration status of parents at follow up</t>
+  </si>
+  <si>
+    <t>Missing sex</t>
+  </si>
+  <si>
+    <t>TRUE</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>FALSE</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Both</t>
+  </si>
+  <si>
+    <t>not specified</t>
+  </si>
+  <si>
+    <t>missing</t>
+  </si>
+  <si>
+    <t>Pre-primary education</t>
+  </si>
+  <si>
+    <t>Upper secondary education</t>
+  </si>
+  <si>
+    <t>Post-secondary non-tertiary education</t>
+  </si>
+  <si>
+    <t>First stage of tertiary education</t>
+  </si>
+  <si>
+    <t>Second stage of tertiary education</t>
+  </si>
+  <si>
+    <t>Don't know</t>
+  </si>
+  <si>
+    <t>Isced-1997 level:Maximum of both parents</t>
+  </si>
+  <si>
+    <t>integer</t>
+  </si>
+  <si>
+    <t>ID_cohort</t>
   </si>
 </sst>
 </file>
@@ -248,7 +265,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -260,9 +277,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -288,7 +302,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -304,9 +318,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -344,9 +358,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -379,26 +393,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -431,26 +428,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -624,8 +604,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31.42578125" customWidth="1"/>
@@ -648,13 +628,13 @@
     </row>
     <row r="2" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>7</v>
+        <v>60</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -665,128 +645,117 @@
         <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="D4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>16</v>
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>58</v>
       </c>
       <c r="D5" t="s">
-        <v>7</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" t="s">
-        <v>54</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>56</v>
+      <c r="C9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B10" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="13" t="s">
-        <v>41</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="B11" s="12" t="s">
+        <v>32</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B12" s="13" t="s">
-        <v>42</v>
+      <c r="B12" s="12" t="s">
+        <v>33</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B13" s="13" t="s">
-        <v>43</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="B14" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>7</v>
+        <v>38</v>
+      </c>
+      <c r="D13" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -797,397 +766,544 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D38"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="9"/>
+    <col min="2" max="2" width="9.140625" style="8"/>
     <col min="3" max="3" width="27.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="D1" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13">
+        <v>6</v>
+      </c>
+      <c r="C13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="9">
+        <v>1</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="9">
+        <v>2</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="9">
+        <v>3</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="9">
+        <v>4</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="9">
+        <v>5</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A20" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="9">
+        <v>6</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="9">
+        <v>7</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="9">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="C22" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="9">
+        <v>9</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="9">
+        <v>10</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B25" s="9">
+        <v>1</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B26" s="9">
+        <v>2</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D26" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" s="9">
+        <v>3</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D27" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B28" s="9">
+        <v>4</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D28" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29" s="9">
         <v>5</v>
       </c>
-      <c r="B3" s="9">
+      <c r="C29" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A30" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B30" s="9">
+        <v>6</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B31" s="9">
+        <v>7</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D31" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B32" s="9">
+        <v>8</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B33" s="9">
+        <v>9</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D33" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B34" s="9">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D34" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" s="10">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D35" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B36" s="10">
+        <v>1</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" s="10">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="10">
-        <v>0</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="10">
+      <c r="C37" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="10">
         <v>1</v>
       </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="10">
-        <v>2</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="10">
-        <v>3</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="10">
-        <v>4</v>
-      </c>
-      <c r="C8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="10">
-        <v>5</v>
-      </c>
-      <c r="C9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="10">
-        <v>6</v>
-      </c>
-      <c r="C10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="10">
-        <v>1</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="10">
-        <v>2</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="10">
-        <v>3</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="10">
-        <v>4</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" s="10">
-        <v>5</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="10">
-        <v>6</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="10">
-        <v>7</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B18" s="10">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7" t="s">
+      <c r="C38" s="5" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="10">
-        <v>9</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="10">
-        <v>10</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B21" s="10">
-        <v>1</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B22" s="10">
-        <v>2</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="10">
-        <v>3</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" s="10">
-        <v>4</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25" s="10">
-        <v>5</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26" s="10">
-        <v>6</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B27" s="10">
-        <v>7</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B28" s="10">
-        <v>8</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B29" s="10">
-        <v>9</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="10">
-        <v>10</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B31" s="11">
-        <v>0</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B32" s="11">
-        <v>1</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B33" s="11">
-        <v>2</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B34" s="11">
-        <v>1</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B35" s="11">
-        <v>0</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>50</v>
+      <c r="D38" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
